--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakvi\Desktop\library_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595D9500-D1E9-4795-B321-C5B26B62D138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A5972-0B42-4EAA-A841-7E771F15A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="1860" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
+    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" firstSheet="2" activeTab="5" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="done" sheetId="6" r:id="rId3"/>
     <sheet name="Partners" sheetId="7" r:id="rId4"/>
     <sheet name="events" sheetId="8" r:id="rId5"/>
-    <sheet name="main page" sheetId="9" r:id="rId6"/>
+    <sheet name="Hero saction" sheetId="9" r:id="rId6"/>
     <sheet name="ჩვენს შესახებ" sheetId="10" r:id="rId7"/>
     <sheet name="Donations" sheetId="11" r:id="rId8"/>
   </sheets>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
   <si>
     <t>Chimpanzee Politics: Power and Sex among Apes</t>
   </si>
@@ -319,15 +319,6 @@
     <t>Partner's web-site</t>
   </si>
   <si>
-    <t>საქართველოს უნივერსიტეტი</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www.ug.ge </t>
-  </si>
-  <si>
-    <t>ჯერ არავინ</t>
-  </si>
-  <si>
     <t>უოლტერ ბლოკი</t>
   </si>
   <si>
@@ -358,15 +349,9 @@
     <t>დასრულებულია. ხელმისაწვდომია გირჩის ოფისში</t>
   </si>
   <si>
-    <t>ბლოკი ლიბერტარიანული ეთიკის პოზიციიდან ანალიზებს საზოგადოების სასჯელის ღირსად მიჩნეულ ადამიანთა ჯგუფებს. გახდა ლიბერტარიანული ფილოსოფიის ერთ-ერთი მნიშვნელოვანი ტექსტი.</t>
-  </si>
-  <si>
     <t>ანოტაცია</t>
   </si>
   <si>
-    <t>როთბარდი ანალიზებს სახელმწიფოს ბუნებას, როგორც ძალდობრივ ინსტიტუტს, რომელიც ინარჩუნებს ძალაუფლებას გადასახადების, კანონისა და იდეოლოგიური ლეგიტიმაციის მეშვეობით.</t>
-  </si>
-  <si>
     <t>გამომცემლობა</t>
   </si>
   <si>
@@ -382,12 +367,6 @@
     <t>მეორე ანოტაცია</t>
   </si>
   <si>
-    <t>page name</t>
-  </si>
-  <si>
-    <t>თბილისის თავისუფლების ბიბლიოთეკა</t>
-  </si>
-  <si>
     <t>event number</t>
   </si>
   <si>
@@ -403,39 +382,15 @@
     <t>event annotation</t>
   </si>
   <si>
-    <t>ყოველწლიური ფილოლოგიური კონფერენცია 2025</t>
-  </si>
-  <si>
-    <t>სამეცნიერო ტერმინოლოგიის დამტკიცება სოციალურ მეცნიერებებში. ღია სესია ყველა დაინტერესებული პირისთვის.</t>
-  </si>
-  <si>
     <t>საქართველოს უნივერსიტეტი, აუდიტორია 525</t>
   </si>
   <si>
-    <t xml:space="preserve">25 ოქტომბევრი 2026 </t>
-  </si>
-  <si>
-    <t>ოპენგეიმერის წიგნის "სახელმწიფო" პრეზენტაცია</t>
-  </si>
-  <si>
     <t>14 ივნისი 2026</t>
   </si>
   <si>
     <t>წიგნის პრეზენტაცია</t>
   </si>
   <si>
-    <t>ლისონის წიგნის პრეზენტაცია</t>
-  </si>
-  <si>
-    <t>საქართველოს უნივერსიტეტი, დიდი დარბაზი</t>
-  </si>
-  <si>
-    <t>ანოტაცია 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 ნოემბერი 2026 </t>
-  </si>
-  <si>
     <t>mission</t>
   </si>
   <si>
@@ -445,23 +400,1321 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>თავისუფლების ბიბლიოთეკა არის არაკომერციული პროექტი, რომლის მიზანია ქართული მეცნიერული ენის განვითარება სოციალურ და ჰუმანიტარულ მეცნიერებებში ცნობილი ნაშრომების თარგმნის მეშვეობით. თითოეული წიგნი არა მხოლოდ ამრავლებს ქართულ ენაზე ხელმისაწვდომ ლიტერატურას, არამედ ასევე აყალიბებს ცალკეული ტერმინების თარგმანს, რომლებიც ყოველწლიურ ფილოლოგიურ კონფერენციაზე მტკიცდება.</t>
-  </si>
-  <si>
-    <t>ჩვენს შესახებ</t>
-  </si>
-  <si>
-    <t>ეს არის ტექსტი ჩვენს შესახებ</t>
-  </si>
-  <si>
-    <t>თქვენი შემოწირულება ფინანსავს მთარგმნელებს, რედაქტორებს და ქართული სამეცნიერო ენის გრძელვადიან განვითარებას.</t>
+    <r>
+      <t>ეპატაჟურ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ნაწარმოებში</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>რომელიც</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>გამოიცა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>აშშ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ში</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 40 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>წლის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>წინ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>პროფესორი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>უოლტერ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ბლოკი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ლიბერტარიანული</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ეთიკისა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>და</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მიუკერძოებელი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ლოგიკის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>პოზიციებიდან</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>იკვლევს</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>საზოგადოების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მიერ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>დევნილი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ტიპაჟებს</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>რომელთა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>შორისაც</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>არიან</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სუტენიორი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მეძავი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ბარაკების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მეპატრონე</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>შანტაჟისტი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მევახშე</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ცილისმწამებელი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ნარკორეალიზატორი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სპეკულანტი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>შუამავალი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>და</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სხვები</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ანალიზის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>შედეგები</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>აოცებს</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>თავისი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სითამამით</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>და</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>პარადოქსულობით</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>დაცვა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ვერდასაცავისა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>უდავოდ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ინტელექტუალური</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>გამოწვევაა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ეკონომისტების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სოციოლოგების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>პოლიტიკოსების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>იურისტებისა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>და</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ფსიქოლოგებისათვის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>წიგნი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>საინტერესოა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>ფართო</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მკითხველისთვისაც</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>რომლებსაც</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>შეუძლიათ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>სტერეოტიპული</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>აღქმის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მოშორება</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>და</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მიუკერძოებელი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>აზროვნების</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>მოძრაობას</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Sylfaen"/>
+        <family val="1"/>
+      </rPr>
+      <t>გაყოლა</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>მიურეი როთბარდის ერთ-ერთი ყველაზე ცნობილი ნაშრომი, რომელიც მკითხველს აჩვენებს, თუ რა არის სახელმწიფო, როგორ წარმოიშვა ის და რისთვის არსებობს.</t>
+  </si>
+  <si>
+    <t>დასრულებულია. ხელმისაწვდომია გირჩის ოფისში და საიტზე mises.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude, see below Donation text </t>
+  </si>
+  <si>
+    <t>თუ გსურთ მხარი დაუჭიროთ პროექტს:</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>BOG</t>
+  </si>
+  <si>
+    <t>Bitcoin</t>
+  </si>
+  <si>
+    <t>GE59BG0000000740227700</t>
+  </si>
+  <si>
+    <t>GE44TB7038445064300044</t>
+  </si>
+  <si>
+    <t>bc1qtzvernqf7ee693jc5qjzec00mk3rg5zmx5hruu</t>
+  </si>
+  <si>
+    <t>წიგნიერება არის ქართული მეცნიერული ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბებაა. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭრო ტერმინების თარგმანი მეცნიერული კონფერეცნიის ფორმატში ფილოლოგების განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართულ მეცნიერული ენის გამდიდრებას შეუწყობს ხელს და დაეხმარება მკლევარებსა მომავალში ქართულად ჩანოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
+  </si>
+  <si>
+    <t>პროექტის პრეზენტაცია</t>
+  </si>
+  <si>
+    <t>პირველი სპონსორი</t>
+  </si>
+  <si>
+    <t>girchi.com</t>
+  </si>
+  <si>
+    <t>მეორე სპონსორი</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.google.com </t>
+  </si>
+  <si>
+    <t>Partners number</t>
+  </si>
+  <si>
+    <t>მესამე სპონსორი</t>
+  </si>
+  <si>
+    <t>წიგნიერების პროექტის ავტორია საქართველოს უნივერსიტეტის პროფესორი სანდრო რაქვიაშვილი. ის ფინანსდება კერძო შემოწირულობებით და პარტნიორების მხარდაჭერით.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">წიგნიერება. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ქართული მეცნიერული ენის განვითარების პროექტი</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -531,10 +1784,17 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFA5D6FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -585,7 +1845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -626,11 +1886,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1467,7 +2726,7 @@
         <v>89</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
@@ -1487,7 +2746,7 @@
         <v>0.01</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -1507,7 +2766,7 @@
         <v>0.02</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1560,50 +2819,50 @@
         <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:9" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
         <v>103</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" t="s">
         <v>106</v>
       </c>
-      <c r="H3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:9" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>86</v>
@@ -1612,16 +2871,16 @@
         <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" t="s">
         <v>106</v>
-      </c>
-      <c r="H4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I4" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1634,11 +2893,14 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
     <col min="2" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
       <c r="B1" t="s">
         <v>92</v>
       </c>
@@ -1651,10 +2913,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1662,7 +2924,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>136</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1670,12 +2935,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>139</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{36ECD84B-D942-43A2-B2AA-D313AAF5FACB}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{0B729D4D-FD53-4444-971B-51F5D35EA191}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{D033FB53-A940-4595-AB02-739DB8242D7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1685,22 +2954,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01312731-008A-4C85-968D-45FF55658C9C}">
   <dimension ref="A2:E5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1708,51 +2980,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
+      <c r="B5" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1761,53 +3010,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ADEECD-0800-47AA-9359-25EC843DD15A}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="16.75" customWidth="1"/>
+    <col min="1" max="2" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="15"/>
-    </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="15"/>
-    </row>
-    <row r="17" spans="1:1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="16"/>
-    </row>
-    <row r="18" spans="1:1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="15"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1821,33 +3049,54 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="13"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" location="about" display="about" xr:uid="{008B27DD-6F91-4C80-A734-62A9820F92B5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33CE8E1-5A15-491E-828B-895952A16214}">
-  <dimension ref="A2"/>
+  <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakvi\Desktop\library_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A5972-0B42-4EAA-A841-7E771F15A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ED641A-76E9-40D9-8570-48126D58FDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" firstSheet="2" activeTab="5" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
+    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="4" r:id="rId1"/>
@@ -18,9 +18,8 @@
     <sheet name="done" sheetId="6" r:id="rId3"/>
     <sheet name="Partners" sheetId="7" r:id="rId4"/>
     <sheet name="events" sheetId="8" r:id="rId5"/>
-    <sheet name="Hero saction" sheetId="9" r:id="rId6"/>
-    <sheet name="ჩვენს შესახებ" sheetId="10" r:id="rId7"/>
-    <sheet name="Donations" sheetId="11" r:id="rId8"/>
+    <sheet name="Hero section" sheetId="9" r:id="rId6"/>
+    <sheet name="Donations" sheetId="11" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Plan!#REF!</definedName>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="141">
   <si>
     <t>Chimpanzee Politics: Power and Sex among Apes</t>
   </si>
@@ -349,9 +348,6 @@
     <t>დასრულებულია. ხელმისაწვდომია გირჩის ოფისში</t>
   </si>
   <si>
-    <t>ანოტაცია</t>
-  </si>
-  <si>
     <t>გამომცემლობა</t>
   </si>
   <si>
@@ -394,9 +390,6 @@
     <t>mission</t>
   </si>
   <si>
-    <t>hero saction</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -1668,9 +1661,6 @@
     <t>bc1qtzvernqf7ee693jc5qjzec00mk3rg5zmx5hruu</t>
   </si>
   <si>
-    <t>წიგნიერება არის ქართული მეცნიერული ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბებაა. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭრო ტერმინების თარგმანი მეცნიერული კონფერეცნიის ფორმატში ფილოლოგების განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართულ მეცნიერული ენის გამდიდრებას შეუწყობს ხელს და დაეხმარება მკლევარებსა მომავალში ქართულად ჩანოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
-  </si>
-  <si>
     <t>პროექტის პრეზენტაცია</t>
   </si>
   <si>
@@ -1692,7 +1682,10 @@
     <t>მესამე სპონსორი</t>
   </si>
   <si>
-    <t>წიგნიერების პროექტის ავტორია საქართველოს უნივერსიტეტის პროფესორი სანდრო რაქვიაშვილი. ის ფინანსდება კერძო შემოწირულობებით და პარტნიორების მხარდაჭერით.</t>
+    <t>hero section</t>
+  </si>
+  <si>
+    <t>Book annotation</t>
   </si>
   <si>
     <r>
@@ -1706,8 +1699,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ქართული მეცნიერული ენის განვითარების პროექტი</t>
-    </r>
+      <t>ქართული სამეცნიერო ენის განვითარების პროექტი</t>
+    </r>
+  </si>
+  <si>
+    <t>წიგნიერება არის ქართული სამეცნიერო ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბებაა. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭრო ტერმინების თარგმანი აკადემიური კონფერეცნიის ფორმატში განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართულ სამეცნიერო ენის გამდიდრებას შეუწყობს ხელს და  მკლევარებს დაეხმარება მომავალში ქართულად ჩანოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2722,7 @@
         <v>89</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
@@ -2746,7 +2742,7 @@
         <v>0.01</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -2766,7 +2762,7 @@
         <v>0.02</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2825,10 +2821,10 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="18" x14ac:dyDescent="0.25">
@@ -2851,10 +2847,10 @@
         <v>103</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="18" x14ac:dyDescent="0.25">
@@ -2874,13 +2870,13 @@
         <v>101</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2899,7 +2895,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
         <v>92</v>
@@ -2913,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2924,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2935,10 +2931,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2960,19 +2956,19 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
         <v>110</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>111</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>112</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>113</v>
-      </c>
-      <c r="E2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2980,16 +2976,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
         <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3018,23 +3014,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3043,60 +3039,42 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C19EC67-93A9-46AA-9536-DDB6AE277099}">
-  <dimension ref="A2:B11"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="13"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33CE8E1-5A15-491E-828B-895952A16214}">
   <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
         <v>127</v>
-      </c>
-      <c r="B5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakvi\Desktop\library_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ED641A-76E9-40D9-8570-48126D58FDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14CCE4A-869C-4637-AAE0-99F8084E2E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
+    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" activeTab="4" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="138">
   <si>
     <t>Chimpanzee Politics: Power and Sex among Apes</t>
   </si>
@@ -381,9 +381,6 @@
     <t>საქართველოს უნივერსიტეტი, აუდიტორია 525</t>
   </si>
   <si>
-    <t>14 ივნისი 2026</t>
-  </si>
-  <si>
     <t>წიგნის პრეზენტაცია</t>
   </si>
   <si>
@@ -1661,27 +1658,15 @@
     <t>bc1qtzvernqf7ee693jc5qjzec00mk3rg5zmx5hruu</t>
   </si>
   <si>
-    <t>პროექტის პრეზენტაცია</t>
-  </si>
-  <si>
     <t>პირველი სპონსორი</t>
   </si>
   <si>
-    <t>girchi.com</t>
-  </si>
-  <si>
-    <t>მეორე სპონსორი</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www.google.com </t>
+    <t>google.com</t>
   </si>
   <si>
     <t>Partners number</t>
   </si>
   <si>
-    <t>მესამე სპონსორი</t>
-  </si>
-  <si>
     <t>hero section</t>
   </si>
   <si>
@@ -1704,6 +1689,12 @@
   </si>
   <si>
     <t>წიგნიერება არის ქართული სამეცნიერო ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბებაა. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭრო ტერმინების თარგმანი აკადემიური კონფერეცნიის ფორმატში განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართულ სამეცნიერო ენის გამდიდრებას შეუწყობს ხელს და  მკლევარებს დაეხმარება მომავალში ქართულად ჩანოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
+  </si>
+  <si>
+    <t>წიგნის პრეზენტაცია. ჰაიეკი. გზა ბატონყმობისკენ</t>
+  </si>
+  <si>
+    <t>14 ივლისი 2026</t>
   </si>
 </sst>
 </file>
@@ -2821,7 +2812,7 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>104</v>
@@ -2847,7 +2838,7 @@
         <v>103</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
         <v>105</v>
@@ -2870,10 +2861,10 @@
         <v>101</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" t="s">
         <v>105</v>
@@ -2895,7 +2886,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s">
         <v>92</v>
@@ -2909,39 +2900,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>134</v>
-      </c>
+      <c r="C3" s="13"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>134</v>
-      </c>
+      <c r="C4" s="13"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{0B729D4D-FD53-4444-971B-51F5D35EA191}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{D033FB53-A940-4595-AB02-739DB8242D7E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2976,16 +2947,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3014,23 +2985,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3045,36 +3016,36 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakvi\Desktop\library_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14CCE4A-869C-4637-AAE0-99F8084E2E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBC84B5-1381-4E7E-841E-2689D84428FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1785" windowWidth="17070" windowHeight="11295" activeTab="4" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
+    <workbookView xWindow="11250" yWindow="1890" windowWidth="17070" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{1C729654-E514-564C-8D1C-FFB207FB8349}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="4" r:id="rId1"/>
@@ -1688,13 +1688,13 @@
     </r>
   </si>
   <si>
-    <t>წიგნიერება არის ქართული სამეცნიერო ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბებაა. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭრო ტერმინების თარგმანი აკადემიური კონფერეცნიის ფორმატში განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართულ სამეცნიერო ენის გამდიდრებას შეუწყობს ხელს და  მკლევარებს დაეხმარება მომავალში ქართულად ჩანოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
-  </si>
-  <si>
     <t>წიგნის პრეზენტაცია. ჰაიეკი. გზა ბატონყმობისკენ</t>
   </si>
   <si>
     <t>14 ივლისი 2026</t>
+  </si>
+  <si>
+    <t>წიგნიერება არის ქართული სამეცნიერო ენის განვითარების პროექტი, რომლის მიზანია ქართული მეცნიერული ტერმინოლოგიის ჩამოყალიბება. მიზნის მისაღწევად სოციალურ და ჰუმანიტარულ მეცნიერებში ცნობილი წიგნების თარგმნა ხორციელდება და ამ პროცესში საჭირო ტერმინების თარგმანი აკადემიური კონფერენციის ფორმატში განხილვის ობიექტად იქცევა. ამ ტერმინების თარგმნა, განხილვა და შემდგომი პრაქტიკაში დანერგვა ქართული სამეცნიერო ენის გამდიდრებას შეუწყობს ხელს და  მკლევარებს დაეხმარება მომავალში ქართულად ჩამოაყალიბონ და განავითარონ საკუთარი იდეები, თეორიები და კონცეფციები.</t>
   </si>
 </sst>
 </file>
@@ -2947,10 +2947,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
         <v>136</v>
-      </c>
-      <c r="C3" t="s">
-        <v>137</v>
       </c>
       <c r="D3" t="s">
         <v>114</v>
@@ -2996,7 +2996,7 @@
         <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
